--- a/testing_reports/excel_spreadsheets/Functionality_Testing_Report.xlsx
+++ b/testing_reports/excel_spreadsheets/Functionality_Testing_Report.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Saveetha Dental College &amp; Hospital  •  Generated: 14 July 2026  |  14:38:13 (100% API Verification Pass)</t>
+          <t>Saveetha Dental College &amp; Hospital  •  Generated: 14 July 2026  |  17:16:18 (100% API Verification Pass)</t>
         </is>
       </c>
     </row>
